--- a/docs/project-management/Trading_Platform_Project_Plan.xlsx
+++ b/docs/project-management/Trading_Platform_Project_Plan.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Dashboard" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Business Req" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional Req" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFRs" sheetId="4" state="visible" r:id="rId4"/>
@@ -20,11 +20,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprints" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gantt" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestone Tracker" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAID" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Plan" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current State" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stakeholder Register" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RACI Matrix" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integrated Delivery Plan" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resource Capacity" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Governance" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Control" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TPM Scenarios" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Business Req'!$A$1:$H$9</definedName>
@@ -32,18 +39,25 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NFRs'!$A$1:$E$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Data Sources'!$A$1:$N$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Data Dictionary'!$A$1:$R$139</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Epics'!$A$1:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Epics'!$A$1:$E$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Stories'!$A$1:$O$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Subtasks'!$A$1:$E$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Acceptance Criteria'!$A$1:$D$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Dependencies'!$A$1:$F$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Sprints'!$A$1:$I$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Gantt'!$A$1:$M$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Milestones'!$A$1:$G$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'RAID'!$A$1:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Sprints'!$A$1:$L$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Gantt'!$A$1:$R$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Milestone Tracker'!$A$1:$I$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'RAID'!$A$1:$K$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Traceability'!$A$1:$F$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Test Plan'!$A$1:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Current State'!$A$1:$E$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Stakeholder Register'!$A$1:$F$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'RACI Matrix'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Integrated Delivery Plan'!$A$1:$J$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Resource Capacity'!$A$1:$F$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Governance'!$A$1:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Change Control'!$A$1:$J$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'TPM Scenarios'!$A$1:$J$4</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -54,7 +68,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode=";;;"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,8 +103,18 @@
       <color rgb="00233746"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="0016324F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0016324F"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -112,6 +136,16 @@
         <fgColor rgb="00007C78"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAF0E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E9ECEF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -130,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -159,12 +193,22 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -199,12 +243,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="00007C78"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00007C78"/>
+          <fgColor rgb="00D8DEE3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -570,25 +611,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="68" customWidth="1" min="3" max="3"/>
+    <col width="75" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="66" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TRADING PLATFORM | DELIVERY PLAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>TRADING PLATFORM | EXECUTIVE PROJECT DASHBOARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Evidence baseline</t>
@@ -596,7 +637,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14; repository + docs/test_results.md dated 2026-10-11</t>
+          <t>2026-10-14; repository plus dated run evidence 2026-10-11</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr"/>
@@ -604,7 +645,7 @@
       <c r="E2" s="3" t="inlineStr"/>
       <c r="F2" s="3" t="inlineStr"/>
     </row>
-    <row r="3">
+    <row r="3" ht="36" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Purpose</t>
@@ -620,123 +661,219 @@
       <c r="E3" s="5" t="inlineStr"/>
       <c r="F3" s="5" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Current implementation</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Six-task Databricks Workflow; 10 Delta tables in cibc.bronze/silver/gold; synthetic trades; Yahoo Finance prices; position/P&amp;L; audit/rejects; notebooks/SQL.</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Current position</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Evidence / caveat</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Decision owner</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Next action</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Not implemented / not evidenced</t>
+          <t>Overall project status</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Deployed dashboard; approved market-data contract; non-dev Bundle targets/CI; automated alerting; production identity; approved retention/RTO/RPO; successful second same-input Databricks run.</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Working technical proof of concept demonstrated; not a production banking implementation.</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Six-task dev Job and 2026-10-11 run evidence; production controls and source approval remain open.</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Role TBD</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>See decisions and RAID</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Scope status</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Proposed 8-week / four 2-week sprints. 40 story points at assumed 10 points per sprint; no capacity reserve. Relative weeks only, not approved calendar dates.</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>USD cash-equity prototype is implemented; enterprise source, lifecycle, FX and accounting scope are not baselined.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>README assumptions and source contracts.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Role TBD</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>See decisions and RAID</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Prototype limitation</t>
+          <t>Schedule status</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>USD cash equities; ten in-code instruments; approximate NYSE calendar; full-history recompute; simplified daily P&amp;L; fees, FX, corporate actions, dividends, settlement cash, and short-sale mechanics excluded.</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Proposed relative 8-week plan only; no kickoff date or actual sprint progress is evidenced.</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>No project execution schedule/actual dates in repository.</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Role TBD</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>See decisions and RAID</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Jira import</t>
+          <t>Quality status</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Temporary planning IDs; map planning key to custom field, issue hierarchy and Epic Link to Jira fields, and replace planning Epic Link values with created Jira epic keys where required.</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Status legend</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>IMPLEMENTED = code/config/test/run evidence; PARTIALLY IMPLEMENTED = supporting behavior with a material gap; PLANNED = not delivered; TO BE CONFIRMED = evidence/owner absent.</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Focused run found 3 stale DDL-path test failures; full-suite result and same-input Databricks rerun are not verified.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>tests reference removed *_constraints.sql; docs/test_results.md second run queued.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Role TBD</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>See decisions and RAID</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Resource status</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Role capacities are planning assumptions; no named assignments or availability commitments are evidenced.</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Proposed capacity plan only.</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Role TBD</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>See decisions and RAID</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Planning metric</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Interpretation</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr"/>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Business requirements</t>
@@ -755,7 +892,7 @@
       <c r="E11" s="5" t="inlineStr"/>
       <c r="F11" s="5" t="inlineStr"/>
     </row>
-    <row r="12">
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Functional requirements</t>
@@ -767,93 +904,594 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Detailed system behaviors</t>
+          <t>Thirteen functional behaviors</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr"/>
       <c r="E12" s="3" t="inlineStr"/>
       <c r="F12" s="3" t="inlineStr"/>
     </row>
-    <row r="13">
+    <row r="13" ht="36" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Jira epics</t>
+          <t>Jira epics / stories / subtasks</t>
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTA(Epics!A:A)-1</f>
+        <f>COUNTA(Epics!A:A)-1&amp;" / "&amp;(COUNTA(Stories!A:A)-1)&amp;" / "&amp;(COUNTA(Subtasks!A:A)-1)</f>
         <v/>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Planning hierarchy</t>
+          <t>Temporary planning IDs</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="inlineStr"/>
       <c r="F13" s="5" t="inlineStr"/>
     </row>
-    <row r="14">
+    <row r="14" ht="36" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Jira stories</t>
+          <t>Total estimated backlog points</t>
         </is>
       </c>
       <c r="B14" s="3">
-        <f>COUNTA(Stories!A:A)-1</f>
+        <f>SUM(Stories!G2:G100)</f>
         <v/>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Includes current-state and proposed work</t>
+          <t>Includes already implemented/reference scope; not remaining effort</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr"/>
       <c r="E14" s="3" t="inlineStr"/>
       <c r="F14" s="3" t="inlineStr"/>
     </row>
-    <row r="15">
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Planned sprint points</t>
+          <t>8-week baseline points / capacity</t>
         </is>
       </c>
       <c r="B15" s="5">
-        <f>SUM(Sprints!E2:E5)</f>
+        <f>SUM(Sprints!G2:G5)&amp;" / "&amp;SUM(Sprints!F2:F5)</f>
         <v/>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Proposed 8-week baseline; no reserve</t>
+          <t>38 SP planned / 40 assumed; 2 SP headroom</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr"/>
       <c r="E15" s="5" t="inlineStr"/>
       <c r="F15" s="5" t="inlineStr"/>
     </row>
-    <row r="16">
+    <row r="16" ht="36" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Physical dictionary columns</t>
+          <t>Optional follow-on points</t>
         </is>
       </c>
       <c r="B16" s="3">
-        <f>COUNTA('Data Dictionary'!G:G)-1</f>
+        <f>Sprints!G6</f>
         <v/>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>DDL-derived across 10 tables</t>
+          <t>Sprint 5 Weeks 9-10; not in baseline</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr"/>
       <c r="E16" s="3" t="inlineStr"/>
       <c r="F16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>DDL dictionary columns</t>
+        </is>
+      </c>
+      <c r="B17" s="5">
+        <f>COUNTA('Data Dictionary'!G:G)-1</f>
+        <v/>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>All 10 physical tables</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Completed deliverables (verified prototype)</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Six-task dev workflow; 10 Delta tables; synthetic 14-column trade CSV; Yahoo Finance adapter; Silver validation/rejects; positions and simplified daily P&amp;L; audit/breaks; two notebooks and SQL.</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Upcoming milestone</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Exit evidence</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Accountable role</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Dependencies</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Approval gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Scope, requirements and trade contract baseline</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>End Week 2</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Approved BR/FR/NFR decisions; trade source/version/correction semantics; named decision owners</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Technical Project Manager / Product Owner</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>TMP-001; TMP-002; TMP-003; TMP-006</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Product Owner and Trade Data Owner; role names proposed, identities TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Source and access design gate</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>End Week 4</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Market-data source decision; target identity/access design; dev workflow gate</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Solution Architect / Market Data Owner</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>TMP-005; TMP-007; TMP-023</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Platform/Security and Market Data Owner; no production access approval assumed</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Engineering controls and trade-history gate</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>End Week 6</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>CI evidence; trade correction/disappearance test; deployment control review</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Lead Data Engineer / Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>TMP-010; TMP-012</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Engineering owner and Product Control review of affected trade semantics</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Prototype acceptance and handover</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>End Week 8</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Supported-runtime tests; same-input rerun; reconciliation/UAT; runbook and support walkthrough</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Product Control / Production Support</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>TMP-016; TMP-021; TMP-022; TMP-024</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Product Control, QA, Production Support, and Sponsor go/no-go for prototype exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Optional dashboard and data sign-off</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>End Week 10 (optional follow-on)</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Approved reporting/data decisions; dashboard reconciliation and role access</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Product Owner / Product Control</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>TMP-008; TMP-014; TMP-020</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Product Owner, Product Control, and access owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Top risks</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Mitigation</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Escalation</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance is not established as an approved or licensed institutional market-data source.</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Market Data Owner</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>No approved provider/rights or completeness owner by source gate.</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Obtain provider/data-rights decision in Sprint 2; keep production scope blocked until approved source is selected.</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Market Data Owner → Sponsor; Security/Legal/Data Governance as applicable.</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Full-snapshot trade Bronze can leave stale Silver trades when trade IDs disappear from later files.</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Trade Data Owner</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>A two-snapshot comparison leaves a trade in Silver after authoritative removal/correction.</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Agree cancellation/deletion semantics and implement two-snapshot reconciliation test before relying on external trade feed.</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Trading Operations and Product Control → Sponsor if semantics affect positions/P&amp;L.</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Full-history recomputation and free-form instrument/book data may not scale or satisfy control expectations.</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Lead Data Engineer</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Representative-volume benchmark exceeds proposed runtime/cost or reference mapping is inconsistent.</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Benchmark representative scale; establish reference ownership and incremental strategy from evidence.</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Lead Engineer / Architect → TPM → Sponsor for scope/capacity decision.</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Eight-week plan has no capacity reserve and depends on part-time approvers and test runtime access.</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Decision/access delay consumes the 2-point baseline headroom or threatens a gate.</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Reserve decision owners at Sprint start; defer dashboard polish or extend by one sprint if critical access/decisions slip.</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>TPM → Sponsor; defer optional dashboard/follow-on or approve added capacity.</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Key dependencies</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Source owners, market-data rights, supported Spark/Delta test runtime, access/security reviewer, Product Control acceptance, support owner.</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="3" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Decisions required</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Approve trade-source owner, delivery contract, completeness/correction/cancellation semantics.</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="inlineStr"/>
+      <c r="D32" s="3" t="inlineStr"/>
+      <c r="E32" s="3" t="inlineStr"/>
+      <c r="F32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Select and approve market-data provider, rights, close definition, SLA and exception owner.</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr"/>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Confirm calculation methodology and tolerance with Product Control; prototype formula is simplified USD cash equity.</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr"/>
+      <c r="C34" s="6" t="inlineStr"/>
+      <c r="D34" s="6" t="inlineStr"/>
+      <c r="E34" s="6" t="inlineStr"/>
+      <c r="F34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Confirm named stakeholders, project capacity, and supported Spark/Delta test environment.</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr"/>
+      <c r="C35" s="5" t="inlineStr"/>
+      <c r="D35" s="5" t="inlineStr"/>
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Approve environment identity, least-privilege access, retention, RTO/RPO, support model and release gate before non-dev use.</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr"/>
+      <c r="C36" s="3" t="inlineStr"/>
+      <c r="D36" s="3" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Confirm dashboard audience/tool; dashboard is blocked pending reporting and access decisions.</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr"/>
+      <c r="C37" s="5" t="inlineStr"/>
+      <c r="D37" s="5" t="inlineStr"/>
+      <c r="E37" s="5" t="inlineStr"/>
+      <c r="F37" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <conditionalFormatting sqref="B5:B37">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>B5="GREEN"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>B5="AMBER"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>B5="RED"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="3">
+      <formula>B5="NOT VERIFIED"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2538,7 +3176,7 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>Sprint 1</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -2570,7 +3208,7 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>Sprint 1</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
@@ -2602,7 +3240,7 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Sprint 1</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -2666,7 +3304,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -2698,7 +3336,7 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -2922,7 +3560,7 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -2954,7 +3592,7 @@
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
@@ -3050,7 +3688,7 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -3178,7 +3816,7 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Sprint 4</t>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -3210,7 +3848,7 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Sprint 4</t>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
@@ -3242,7 +3880,7 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Sprint 4</t>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -3274,7 +3912,7 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>Sprint 4</t>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
@@ -3370,7 +4008,7 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Current/complete</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -3680,18 +4318,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="68" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="68" customWidth="1" min="6" max="6"/>
-    <col width="72" customWidth="1" min="7" max="7"/>
-    <col width="72" customWidth="1" min="8" max="8"/>
-    <col width="72" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="68" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="68" customWidth="1" min="9" max="9"/>
+    <col width="72" customWidth="1" min="10" max="10"/>
+    <col width="72" customWidth="1" min="11" max="11"/>
+    <col width="72" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -3707,35 +4348,50 @@
       </c>
       <c r="C1" s="7" t="inlineStr">
         <is>
+          <t>Plan classification</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
           <t>Sprint goal</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Planned stories</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
-        <is>
-          <t>Story points (formula)</t>
-        </is>
-      </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
+          <t>Capacity (SP)</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Planned SP (formula)</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Headroom / (over) (formula)</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
           <t>Dependencies</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Deliverables</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
-        <is>
-          <t>Demo outcome</t>
-        </is>
-      </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>Demonstration</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>Exit criteria</t>
         </is>
@@ -3754,36 +4410,48 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Lock project scope, requirement acceptance, measurable NFRs, and target access design.</t>
+          <t>8-week baseline</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>TMP-001; TMP-002; TMP-003; TMP-005</t>
-        </is>
-      </c>
-      <c r="E2" s="8">
+          <t>Baseline scope, requirements, NFRs, and trade source semantics; identify decision owners.</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>TMP-001; TMP-002; TMP-003; TMP-006</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" s="8">
         <f>SUMIF(Stories!$J:$J,A2,Stories!$G:$G)</f>
         <v/>
       </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>Kickoff and timely access to business, market-data, and platform decision owners.</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>Approved scope, BR/FR baseline, NFR decision log, target security/environment design.</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>Trace one trade and one price source through implemented modules and show signed acceptance criteria.</t>
-        </is>
+      <c r="H2" s="8">
+        <f>F2-G2</f>
+        <v/>
       </c>
       <c r="I2" s="8" t="inlineStr">
         <is>
-          <t>No critical source, access, calculation, or report requirement remains ownerless.</t>
+          <t>Kickoff; timely access to product, trading operations, and trade-source decision owners.</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>Implementation baseline, BR/FR and NFR decisions, trade source contract and correction semantics.</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>Walk from 14-column synthetic CSV contract to Bronze/Silver rules and show acceptance traceability.</t>
+        </is>
+      </c>
+      <c r="L2" s="8" t="inlineStr">
+        <is>
+          <t>No critical requirement or source decision is ownerless; trade snapshot/correction semantics recorded.</t>
         </is>
       </c>
     </row>
@@ -3800,36 +4468,48 @@
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Resolve market-data decisions, dictionary, price exception handling, and runtime test strategy.</t>
+          <t>8-week baseline</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>TMP-007; TMP-008; TMP-014; TMP-016</t>
-        </is>
-      </c>
-      <c r="E3" s="9">
+          <t>Close target access design, market-data decision, and controlled dev operating procedure.</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>TMP-005; TMP-007; TMP-023</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" s="9">
         <f>SUMIF(Stories!$J:$J,A3,Stories!$G:$G)</f>
         <v/>
       </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 1 approved scope; access to market-data owner; supported Databricks/Spark test environment.</t>
-        </is>
-      </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t>Source decision, DDL-backed dictionary signoff, missing-price procedure, integration/rerun evidence.</t>
-        </is>
-      </c>
-      <c r="H3" s="9" t="inlineStr">
-        <is>
-          <t>Show a missing-session case and typed data/reject outcomes; demonstrate integration suite execution.</t>
-        </is>
+      <c r="H3" s="9">
+        <f>F3-G3</f>
+        <v/>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>Price feed is approved or explicitly remains prototype-only; unresolved runtime/test access has an owner and date.</t>
+          <t>Sprint 1 requirements; platform/security and market-data decision owners.</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>Environment/access design, market-data decision or prototype-only boundary, workflow/schedule gate.</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>Review source-provider decision criteria, Bundle target, permissions, and paused schedule gate.</t>
+        </is>
+      </c>
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>No production source or target is represented as approved without evidence.</t>
         </is>
       </c>
     </row>
@@ -3846,36 +4526,48 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Improve deployment controls and resolve trade snapshot history/correction semantics.</t>
+          <t>8-week baseline</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
+          <t>Establish reviewed CI/deployment controls and resolve trade snapshot correction behavior.</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
           <t>TMP-010; TMP-012</t>
         </is>
       </c>
-      <c r="E4" s="8">
+      <c r="F4" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8">
         <f>SUMIF(Stories!$J:$J,A4,Stories!$G:$G)</f>
         <v/>
       </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>Approved security/environment design; trade owner signs source semantics.</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Reviewed CI and promotion controls; tested correction/disappearance behavior.</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>Show PR checks and a two-snapshot correction/cancellation case.</t>
-        </is>
+      <c r="H4" s="8">
+        <f>F4-G4</f>
+        <v/>
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>Deployment path is reproducible and trade history behavior is explicit/tested.</t>
+          <t>Approved environment design and trade-source semantics from Sprint 1/2.</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>CI and promotion checks; two-snapshot correction/disappearance behavior and test evidence.</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>Show PR checks and a source correction/deletion scenario through position history.</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>A source correction has an explicit rule and a test; deployment promotion remains gated.</t>
         </is>
       </c>
     </row>
@@ -3892,41 +4584,151 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Deliver reporting MVP, reconciliation/UAT evidence, and operations handover.</t>
+          <t>8-week baseline</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>TMP-020; TMP-022; TMP-024</t>
-        </is>
-      </c>
-      <c r="E5" s="9">
+          <t>Close test failures, supported-runtime rerun/reconciliation, and operational handover.</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>TMP-016; TMP-021; TMP-022; TMP-024</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" s="9">
         <f>SUMIF(Stories!$J:$J,A5,Stories!$G:$G)</f>
         <v/>
       </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>Approved reporting requirements, integration evidence, support owner, and prior sprint outputs.</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>Dashboard MVP, signed UAT/reconciliation, runbook and alerting handover.</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>Show dashboard reconciliation from source trade through daily P&amp;L and demonstrate failure recovery.</t>
-        </is>
+      <c r="H5" s="9">
+        <f>F5-G5</f>
+        <v/>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>Product/operations sign-off; no unresolved critical risk; schedule stays paused absent production readiness approval.</t>
+          <t>Supported Spark/Delta runtime, source decisions, test access, and support role participation.</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>Fixed stale DDL test references, integration/idempotency evidence, UAT reconciliation, runbook and handover.</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>Show a rerun comparison, financial reconciliation, and failure-to-recovery walkthrough.</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>Known critical defects closed or explicitly accepted; production schedule remains paused without a separate go-live gate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 5 (Optional)</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Weeks 9-10 (follow-on; not in 8-week baseline)</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Optional follow-on</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Complete follow-on data approval, missing-price operations, dictionary approval, and dashboard MVP if authorized.</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>TMP-008; TMP-014; TMP-020</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="8">
+        <f>SUMIF(Stories!$J:$J,A6,Stories!$G:$G)</f>
+        <v/>
+      </c>
+      <c r="H6" s="8">
+        <f>F6-G6</f>
+        <v/>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Confirmed reporting audience, approved source, retained capacity, and business sign-off.</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Approved data dictionary/retention decisions, price exception procedure, dashboard MVP and reconciliation.</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>Demonstrate a role-controlled dashboard and missing-price drill-through reconciled to Gold.</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>Follow-on scope is approved and dashboard totals/access are accepted; no assumed production go-live.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I5"/>
+  <autoFilter ref="A1:L6"/>
+  <conditionalFormatting sqref="H2">
+    <cfRule type="expression" priority="1" dxfId="2">
+      <formula>H2&lt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>H2&gt;=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>H3&lt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>H3&gt;=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="expression" priority="5" dxfId="2">
+      <formula>H4&lt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="0">
+      <formula>H4&gt;=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5">
+    <cfRule type="expression" priority="7" dxfId="2">
+      <formula>H5&lt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="0">
+      <formula>H5&gt;=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6">
+    <cfRule type="expression" priority="9" dxfId="2">
+      <formula>H6&lt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="0">
+      <formula>H6&gt;=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -3938,86 +4740,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1" ht="42" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Planning ID</t>
+          <t>Activity ID</t>
         </is>
       </c>
       <c r="B1" s="7" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Workstream / task</t>
         </is>
       </c>
       <c r="C1" s="7" t="inlineStr">
         <is>
-          <t>Sprint</t>
+          <t>Jira story IDs</t>
         </is>
       </c>
       <c r="D1" s="7" t="inlineStr">
         <is>
+          <t>Duration basis</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
           <t>Start week</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
-        <is>
-          <t>Duration (weeks)</t>
-        </is>
-      </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
+          <t>Finish week</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Predecessor activity / story IDs</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Implementation evidence status</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Schedule status</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
           <t>Week 1</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>Week 2</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>Week 3</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>Week 4</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>Week 5</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>Week 6</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="Q1" s="7" t="inlineStr">
         <is>
           <t>Week 7</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="R1" s="7" t="inlineStr">
         <is>
           <t>Week 8</t>
         </is>
@@ -4026,758 +4858,997 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>TMP-001</t>
+          <t>WS-01</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Baseline current implementation and confirm scope</t>
+          <t>Requirements and scope</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Sprint 1</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="n">
+          <t>TMP-001; TMP-002; TMP-003</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Two-week sprint allocation window; task-level duration is not specified</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="F2" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F2" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D2,COLUMN()-5&lt;$D2+$E2)</f>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>M-01</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="K2" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E2,COLUMN()-10&lt;=$F2)</f>
         <v/>
       </c>
-      <c r="G2" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D2,COLUMN()-5&lt;$D2+$E2)</f>
+      <c r="L2" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E2,COLUMN()-10&lt;=$F2)</f>
         <v/>
       </c>
-      <c r="H2" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D2,COLUMN()-5&lt;$D2+$E2)</f>
+      <c r="M2" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E2,COLUMN()-10&lt;=$F2)</f>
         <v/>
       </c>
-      <c r="I2" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D2,COLUMN()-5&lt;$D2+$E2)</f>
+      <c r="N2" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E2,COLUMN()-10&lt;=$F2)</f>
         <v/>
       </c>
-      <c r="J2" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D2,COLUMN()-5&lt;$D2+$E2)</f>
+      <c r="O2" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E2,COLUMN()-10&lt;=$F2)</f>
         <v/>
       </c>
-      <c r="K2" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D2,COLUMN()-5&lt;$D2+$E2)</f>
+      <c r="P2" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E2,COLUMN()-10&lt;=$F2)</f>
         <v/>
       </c>
-      <c r="L2" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D2,COLUMN()-5&lt;$D2+$E2)</f>
+      <c r="Q2" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E2,COLUMN()-10&lt;=$F2)</f>
         <v/>
       </c>
-      <c r="M2" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D2,COLUMN()-5&lt;$D2+$E2)</f>
+      <c r="R2" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E2,COLUMN()-10&lt;=$F2)</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>TMP-002</t>
+          <t>WS-02</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>Approve business and functional requirements</t>
+          <t>Trade source contract</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Sprint 1</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="n">
+          <t>TMP-006</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Two-week sprint allocation window; task-level duration is not specified</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="9" t="n">
+      <c r="F3" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D3,COLUMN()-5&lt;$D3+$E3)</f>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>M-01</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="K3" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E3,COLUMN()-10&lt;=$F3)</f>
         <v/>
       </c>
-      <c r="G3" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D3,COLUMN()-5&lt;$D3+$E3)</f>
+      <c r="L3" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E3,COLUMN()-10&lt;=$F3)</f>
         <v/>
       </c>
-      <c r="H3" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D3,COLUMN()-5&lt;$D3+$E3)</f>
+      <c r="M3" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E3,COLUMN()-10&lt;=$F3)</f>
         <v/>
       </c>
-      <c r="I3" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D3,COLUMN()-5&lt;$D3+$E3)</f>
+      <c r="N3" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E3,COLUMN()-10&lt;=$F3)</f>
         <v/>
       </c>
-      <c r="J3" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D3,COLUMN()-5&lt;$D3+$E3)</f>
+      <c r="O3" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E3,COLUMN()-10&lt;=$F3)</f>
         <v/>
       </c>
-      <c r="K3" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D3,COLUMN()-5&lt;$D3+$E3)</f>
+      <c r="P3" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E3,COLUMN()-10&lt;=$F3)</f>
         <v/>
       </c>
-      <c r="L3" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D3,COLUMN()-5&lt;$D3+$E3)</f>
+      <c r="Q3" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E3,COLUMN()-10&lt;=$F3)</f>
         <v/>
       </c>
-      <c r="M3" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D3,COLUMN()-5&lt;$D3+$E3)</f>
+      <c r="R3" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E3,COLUMN()-10&lt;=$F3)</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>TMP-003</t>
+          <t>WS-03</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Set measurable non-functional and operational targets</t>
+          <t>Security and environment design</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Sprint 1</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="n">
-        <v>1</v>
+          <t>TMP-005</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Two-week sprint allocation window; task-level duration is not specified</t>
+        </is>
       </c>
       <c r="E4" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D4,COLUMN()-5&lt;$D4+$E4)</f>
+        <v>3</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>WS-01; TMP-004</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>M-02</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="K4" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E4,COLUMN()-10&lt;=$F4)</f>
         <v/>
       </c>
-      <c r="G4" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D4,COLUMN()-5&lt;$D4+$E4)</f>
+      <c r="L4" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E4,COLUMN()-10&lt;=$F4)</f>
         <v/>
       </c>
-      <c r="H4" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D4,COLUMN()-5&lt;$D4+$E4)</f>
+      <c r="M4" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E4,COLUMN()-10&lt;=$F4)</f>
         <v/>
       </c>
-      <c r="I4" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D4,COLUMN()-5&lt;$D4+$E4)</f>
+      <c r="N4" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E4,COLUMN()-10&lt;=$F4)</f>
         <v/>
       </c>
-      <c r="J4" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D4,COLUMN()-5&lt;$D4+$E4)</f>
+      <c r="O4" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E4,COLUMN()-10&lt;=$F4)</f>
         <v/>
       </c>
-      <c r="K4" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D4,COLUMN()-5&lt;$D4+$E4)</f>
+      <c r="P4" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E4,COLUMN()-10&lt;=$F4)</f>
         <v/>
       </c>
-      <c r="L4" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D4,COLUMN()-5&lt;$D4+$E4)</f>
+      <c r="Q4" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E4,COLUMN()-10&lt;=$F4)</f>
         <v/>
       </c>
-      <c r="M4" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D4,COLUMN()-5&lt;$D4+$E4)</f>
+      <c r="R4" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E4,COLUMN()-10&lt;=$F4)</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>TMP-005</t>
+          <t>WS-04</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Approve target security and environment architecture</t>
+          <t>Market-data provider decision</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Sprint 1</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>1</v>
+          <t>TMP-007</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Two-week sprint allocation window; task-level duration is not specified</t>
+        </is>
       </c>
       <c r="E5" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D5,COLUMN()-5&lt;$D5+$E5)</f>
+        <v>3</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>WS-01</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>M-02</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="K5" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E5,COLUMN()-10&lt;=$F5)</f>
         <v/>
       </c>
-      <c r="G5" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D5,COLUMN()-5&lt;$D5+$E5)</f>
+      <c r="L5" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E5,COLUMN()-10&lt;=$F5)</f>
         <v/>
       </c>
-      <c r="H5" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D5,COLUMN()-5&lt;$D5+$E5)</f>
+      <c r="M5" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E5,COLUMN()-10&lt;=$F5)</f>
         <v/>
       </c>
-      <c r="I5" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D5,COLUMN()-5&lt;$D5+$E5)</f>
+      <c r="N5" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E5,COLUMN()-10&lt;=$F5)</f>
         <v/>
       </c>
-      <c r="J5" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D5,COLUMN()-5&lt;$D5+$E5)</f>
+      <c r="O5" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E5,COLUMN()-10&lt;=$F5)</f>
         <v/>
       </c>
-      <c r="K5" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D5,COLUMN()-5&lt;$D5+$E5)</f>
+      <c r="P5" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E5,COLUMN()-10&lt;=$F5)</f>
         <v/>
       </c>
-      <c r="L5" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D5,COLUMN()-5&lt;$D5+$E5)</f>
+      <c r="Q5" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E5,COLUMN()-10&lt;=$F5)</f>
         <v/>
       </c>
-      <c r="M5" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D5,COLUMN()-5&lt;$D5+$E5)</f>
+      <c r="R5" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E5,COLUMN()-10&lt;=$F5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>TMP-007</t>
+          <t>WS-05</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Select and approve market-data source</t>
+          <t>Workflow and schedule gate</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="n">
+          <t>TMP-023</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Two-week sprint allocation window; task-level duration is not specified</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D6,COLUMN()-5&lt;$D6+$E6)</f>
+      <c r="F6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>TMP-009</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>M-02</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="K6" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E6,COLUMN()-10&lt;=$F6)</f>
         <v/>
       </c>
-      <c r="G6" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D6,COLUMN()-5&lt;$D6+$E6)</f>
+      <c r="L6" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E6,COLUMN()-10&lt;=$F6)</f>
         <v/>
       </c>
-      <c r="H6" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D6,COLUMN()-5&lt;$D6+$E6)</f>
+      <c r="M6" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E6,COLUMN()-10&lt;=$F6)</f>
         <v/>
       </c>
-      <c r="I6" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D6,COLUMN()-5&lt;$D6+$E6)</f>
+      <c r="N6" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E6,COLUMN()-10&lt;=$F6)</f>
         <v/>
       </c>
-      <c r="J6" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D6,COLUMN()-5&lt;$D6+$E6)</f>
+      <c r="O6" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E6,COLUMN()-10&lt;=$F6)</f>
         <v/>
       </c>
-      <c r="K6" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D6,COLUMN()-5&lt;$D6+$E6)</f>
+      <c r="P6" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E6,COLUMN()-10&lt;=$F6)</f>
         <v/>
       </c>
-      <c r="L6" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D6,COLUMN()-5&lt;$D6+$E6)</f>
+      <c r="Q6" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E6,COLUMN()-10&lt;=$F6)</f>
         <v/>
       </c>
-      <c r="M6" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D6,COLUMN()-5&lt;$D6+$E6)</f>
+      <c r="R6" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E6,COLUMN()-10&lt;=$F6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>TMP-008</t>
+          <t>WS-06</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Approve physical data dictionary and retention model</t>
+          <t>CI/CD promotion controls</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>3</v>
+          <t>TMP-010</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Two-week sprint allocation window; task-level duration is not specified</t>
+        </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D7,COLUMN()-5&lt;$D7+$E7)</f>
+        <v>5</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>WS-03; TMP-009</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>M-03</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="K7" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E7,COLUMN()-10&lt;=$F7)</f>
         <v/>
       </c>
-      <c r="G7" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D7,COLUMN()-5&lt;$D7+$E7)</f>
+      <c r="L7" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E7,COLUMN()-10&lt;=$F7)</f>
         <v/>
       </c>
-      <c r="H7" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D7,COLUMN()-5&lt;$D7+$E7)</f>
+      <c r="M7" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E7,COLUMN()-10&lt;=$F7)</f>
         <v/>
       </c>
-      <c r="I7" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D7,COLUMN()-5&lt;$D7+$E7)</f>
+      <c r="N7" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E7,COLUMN()-10&lt;=$F7)</f>
         <v/>
       </c>
-      <c r="J7" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D7,COLUMN()-5&lt;$D7+$E7)</f>
+      <c r="O7" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E7,COLUMN()-10&lt;=$F7)</f>
         <v/>
       </c>
-      <c r="K7" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D7,COLUMN()-5&lt;$D7+$E7)</f>
+      <c r="P7" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E7,COLUMN()-10&lt;=$F7)</f>
         <v/>
       </c>
-      <c r="L7" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D7,COLUMN()-5&lt;$D7+$E7)</f>
+      <c r="Q7" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E7,COLUMN()-10&lt;=$F7)</f>
         <v/>
       </c>
-      <c r="M7" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D7,COLUMN()-5&lt;$D7+$E7)</f>
+      <c r="R7" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E7,COLUMN()-10&lt;=$F7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>TMP-010</t>
+          <t>WS-07</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Add reviewed CI checks and controlled deployment promotion</t>
+          <t>Trade correction and history</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n">
+          <t>TMP-012</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Two-week sprint allocation window; task-level duration is not specified</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D8,COLUMN()-5&lt;$D8+$E8)</f>
+      <c r="F8" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>WS-02; TMP-011</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>M-03</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="K8" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E8,COLUMN()-10&lt;=$F8)</f>
         <v/>
       </c>
-      <c r="G8" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D8,COLUMN()-5&lt;$D8+$E8)</f>
+      <c r="L8" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E8,COLUMN()-10&lt;=$F8)</f>
         <v/>
       </c>
-      <c r="H8" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D8,COLUMN()-5&lt;$D8+$E8)</f>
+      <c r="M8" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E8,COLUMN()-10&lt;=$F8)</f>
         <v/>
       </c>
-      <c r="I8" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D8,COLUMN()-5&lt;$D8+$E8)</f>
+      <c r="N8" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E8,COLUMN()-10&lt;=$F8)</f>
         <v/>
       </c>
-      <c r="J8" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D8,COLUMN()-5&lt;$D8+$E8)</f>
+      <c r="O8" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E8,COLUMN()-10&lt;=$F8)</f>
         <v/>
       </c>
-      <c r="K8" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D8,COLUMN()-5&lt;$D8+$E8)</f>
+      <c r="P8" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E8,COLUMN()-10&lt;=$F8)</f>
         <v/>
       </c>
-      <c r="L8" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D8,COLUMN()-5&lt;$D8+$E8)</f>
+      <c r="Q8" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E8,COLUMN()-10&lt;=$F8)</f>
         <v/>
       </c>
-      <c r="M8" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D8,COLUMN()-5&lt;$D8+$E8)</f>
+      <c r="R8" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E8,COLUMN()-10&lt;=$F8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>TMP-012</t>
+          <t>WS-08</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Resolve trade snapshot disappearance and historical correction controls</t>
+          <t>Spark/Delta rerun validation</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>5</v>
+          <t>TMP-016</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Two-week sprint allocation window; task-level duration is not specified</t>
+        </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D9,COLUMN()-5&lt;$D9+$E9)</f>
+        <v>7</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>TMP-015</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>M-04</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="K9" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E9,COLUMN()-10&lt;=$F9)</f>
         <v/>
       </c>
-      <c r="G9" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D9,COLUMN()-5&lt;$D9+$E9)</f>
+      <c r="L9" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E9,COLUMN()-10&lt;=$F9)</f>
         <v/>
       </c>
-      <c r="H9" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D9,COLUMN()-5&lt;$D9+$E9)</f>
+      <c r="M9" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E9,COLUMN()-10&lt;=$F9)</f>
         <v/>
       </c>
-      <c r="I9" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D9,COLUMN()-5&lt;$D9+$E9)</f>
+      <c r="N9" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E9,COLUMN()-10&lt;=$F9)</f>
         <v/>
       </c>
-      <c r="J9" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D9,COLUMN()-5&lt;$D9+$E9)</f>
+      <c r="O9" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E9,COLUMN()-10&lt;=$F9)</f>
         <v/>
       </c>
-      <c r="K9" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D9,COLUMN()-5&lt;$D9+$E9)</f>
+      <c r="P9" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E9,COLUMN()-10&lt;=$F9)</f>
         <v/>
       </c>
-      <c r="L9" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D9,COLUMN()-5&lt;$D9+$E9)</f>
+      <c r="Q9" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E9,COLUMN()-10&lt;=$F9)</f>
         <v/>
       </c>
-      <c r="M9" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D9,COLUMN()-5&lt;$D9+$E9)</f>
+      <c r="R9" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E9,COLUMN()-10&lt;=$F9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>TMP-014</t>
+          <t>WS-09</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Harden price source decision and completeness exception process</t>
+          <t>Test maintenance and QA</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>3</v>
+          <t>TMP-021</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Two-week sprint allocation window; task-level duration is not specified</t>
+        </is>
       </c>
       <c r="E10" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D10,COLUMN()-5&lt;$D10+$E10)</f>
+        <v>7</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>M-04</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="K10" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E10,COLUMN()-10&lt;=$F10)</f>
         <v/>
       </c>
-      <c r="G10" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D10,COLUMN()-5&lt;$D10+$E10)</f>
+      <c r="L10" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E10,COLUMN()-10&lt;=$F10)</f>
         <v/>
       </c>
-      <c r="H10" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D10,COLUMN()-5&lt;$D10+$E10)</f>
+      <c r="M10" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E10,COLUMN()-10&lt;=$F10)</f>
         <v/>
       </c>
-      <c r="I10" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D10,COLUMN()-5&lt;$D10+$E10)</f>
+      <c r="N10" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E10,COLUMN()-10&lt;=$F10)</f>
         <v/>
       </c>
-      <c r="J10" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D10,COLUMN()-5&lt;$D10+$E10)</f>
+      <c r="O10" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E10,COLUMN()-10&lt;=$F10)</f>
         <v/>
       </c>
-      <c r="K10" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D10,COLUMN()-5&lt;$D10+$E10)</f>
+      <c r="P10" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E10,COLUMN()-10&lt;=$F10)</f>
         <v/>
       </c>
-      <c r="L10" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D10,COLUMN()-5&lt;$D10+$E10)</f>
+      <c r="Q10" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E10,COLUMN()-10&lt;=$F10)</f>
         <v/>
       </c>
-      <c r="M10" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D10,COLUMN()-5&lt;$D10+$E10)</f>
+      <c r="R10" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E10,COLUMN()-10&lt;=$F10)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>TMP-016</t>
+          <t>WS-10</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Run Spark/Delta integration and end-to-end rerun validation</t>
+          <t>Reconciliation and UAT</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>3</v>
+          <t>TMP-022</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Two-week sprint allocation window; task-level duration is not specified</t>
+        </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D11,COLUMN()-5&lt;$D11+$E11)</f>
+        <v>7</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>WS-08; TMP-018</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>M-04</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="K11" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E11,COLUMN()-10&lt;=$F11)</f>
         <v/>
       </c>
-      <c r="G11" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D11,COLUMN()-5&lt;$D11+$E11)</f>
+      <c r="L11" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E11,COLUMN()-10&lt;=$F11)</f>
         <v/>
       </c>
-      <c r="H11" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D11,COLUMN()-5&lt;$D11+$E11)</f>
+      <c r="M11" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E11,COLUMN()-10&lt;=$F11)</f>
         <v/>
       </c>
-      <c r="I11" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D11,COLUMN()-5&lt;$D11+$E11)</f>
+      <c r="N11" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E11,COLUMN()-10&lt;=$F11)</f>
         <v/>
       </c>
-      <c r="J11" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D11,COLUMN()-5&lt;$D11+$E11)</f>
+      <c r="O11" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E11,COLUMN()-10&lt;=$F11)</f>
         <v/>
       </c>
-      <c r="K11" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D11,COLUMN()-5&lt;$D11+$E11)</f>
+      <c r="P11" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E11,COLUMN()-10&lt;=$F11)</f>
         <v/>
       </c>
-      <c r="L11" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D11,COLUMN()-5&lt;$D11+$E11)</f>
+      <c r="Q11" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E11,COLUMN()-10&lt;=$F11)</f>
         <v/>
       </c>
-      <c r="M11" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D11,COLUMN()-5&lt;$D11+$E11)</f>
+      <c r="R11" s="12">
+        <f>--AND(COLUMN()-10&gt;=$E11,COLUMN()-10&lt;=$F11)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>TMP-020</t>
+          <t>WS-11</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Deliver user-accepted trading and P&amp;L dashboard MVP</t>
+          <t>Operations handover</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="n">
+          <t>TMP-024</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Two-week sprint allocation window; task-level duration is not specified</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="E12" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D12,COLUMN()-5&lt;$D12+$E12)</f>
+      <c r="F12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>WS-01; WS-05; WS-10; TMP-019</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>M-04</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="K12" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E12,COLUMN()-10&lt;=$F12)</f>
         <v/>
       </c>
-      <c r="G12" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D12,COLUMN()-5&lt;$D12+$E12)</f>
+      <c r="L12" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E12,COLUMN()-10&lt;=$F12)</f>
         <v/>
       </c>
-      <c r="H12" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D12,COLUMN()-5&lt;$D12+$E12)</f>
+      <c r="M12" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E12,COLUMN()-10&lt;=$F12)</f>
         <v/>
       </c>
-      <c r="I12" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D12,COLUMN()-5&lt;$D12+$E12)</f>
+      <c r="N12" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E12,COLUMN()-10&lt;=$F12)</f>
         <v/>
       </c>
-      <c r="J12" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D12,COLUMN()-5&lt;$D12+$E12)</f>
+      <c r="O12" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E12,COLUMN()-10&lt;=$F12)</f>
         <v/>
       </c>
-      <c r="K12" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D12,COLUMN()-5&lt;$D12+$E12)</f>
+      <c r="P12" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E12,COLUMN()-10&lt;=$F12)</f>
         <v/>
       </c>
-      <c r="L12" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D12,COLUMN()-5&lt;$D12+$E12)</f>
+      <c r="Q12" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E12,COLUMN()-10&lt;=$F12)</f>
         <v/>
       </c>
-      <c r="M12" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D12,COLUMN()-5&lt;$D12+$E12)</f>
+      <c r="R12" s="11">
+        <f>--AND(COLUMN()-10&gt;=$E12,COLUMN()-10&lt;=$F12)</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>TMP-022</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Complete independent position/P&amp;L reconciliation and UAT</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D13,COLUMN()-5&lt;$D13+$E13)</f>
-        <v/>
-      </c>
-      <c r="G13" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D13,COLUMN()-5&lt;$D13+$E13)</f>
-        <v/>
-      </c>
-      <c r="H13" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D13,COLUMN()-5&lt;$D13+$E13)</f>
-        <v/>
-      </c>
-      <c r="I13" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D13,COLUMN()-5&lt;$D13+$E13)</f>
-        <v/>
-      </c>
-      <c r="J13" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D13,COLUMN()-5&lt;$D13+$E13)</f>
-        <v/>
-      </c>
-      <c r="K13" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D13,COLUMN()-5&lt;$D13+$E13)</f>
-        <v/>
-      </c>
-      <c r="L13" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D13,COLUMN()-5&lt;$D13+$E13)</f>
-        <v/>
-      </c>
-      <c r="M13" s="11">
-        <f>--AND(COLUMN()-5&gt;=$D13,COLUMN()-5&lt;$D13+$E13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>TMP-024</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Create support runbook, alerting, and handover</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D14,COLUMN()-5&lt;$D14+$E14)</f>
-        <v/>
-      </c>
-      <c r="G14" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D14,COLUMN()-5&lt;$D14+$E14)</f>
-        <v/>
-      </c>
-      <c r="H14" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D14,COLUMN()-5&lt;$D14+$E14)</f>
-        <v/>
-      </c>
-      <c r="I14" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D14,COLUMN()-5&lt;$D14+$E14)</f>
-        <v/>
-      </c>
-      <c r="J14" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D14,COLUMN()-5&lt;$D14+$E14)</f>
-        <v/>
-      </c>
-      <c r="K14" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D14,COLUMN()-5&lt;$D14+$E14)</f>
-        <v/>
-      </c>
-      <c r="L14" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D14,COLUMN()-5&lt;$D14+$E14)</f>
-        <v/>
-      </c>
-      <c r="M14" s="10">
-        <f>--AND(COLUMN()-5&gt;=$D14,COLUMN()-5&lt;$D14+$E14)</f>
-        <v/>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="14" t="inlineStr"/>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Milestone markers</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr"/>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>Week-end gates</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr"/>
+      <c r="F13" s="14" t="inlineStr"/>
+      <c r="G13" s="14" t="inlineStr"/>
+      <c r="H13" s="14" t="inlineStr"/>
+      <c r="I13" s="14" t="inlineStr"/>
+      <c r="J13" s="14" t="inlineStr"/>
+      <c r="K13" s="14" t="inlineStr"/>
+      <c r="L13" s="14" t="inlineStr">
+        <is>
+          <t>M-01</t>
+        </is>
+      </c>
+      <c r="M13" s="14" t="inlineStr"/>
+      <c r="N13" s="14" t="inlineStr">
+        <is>
+          <t>M-02</t>
+        </is>
+      </c>
+      <c r="O13" s="14" t="inlineStr"/>
+      <c r="P13" s="14" t="inlineStr">
+        <is>
+          <t>M-03</t>
+        </is>
+      </c>
+      <c r="Q13" s="14" t="inlineStr"/>
+      <c r="R13" s="14" t="inlineStr">
+        <is>
+          <t>M-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Scheduling note</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Bars show assigned two-week sprint windows only; they are not task-level durations. No kickoff date, activity duration, resource-levelled calendar, CPM dates, or float is evidenced. Sprint 5 (Weeks 9-10) is optional follow-on and is not plotted.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M14"/>
-  <conditionalFormatting sqref="F2:F14">
+  <autoFilter ref="A1:R15"/>
+  <mergeCells count="1">
+    <mergeCell ref="B15:R15"/>
+  </mergeCells>
+  <conditionalFormatting sqref="K2:R2">
     <cfRule type="expression" priority="1" dxfId="4">
-      <formula>F2=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G14">
-    <cfRule type="expression" priority="2" dxfId="4">
-      <formula>G2=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H14">
-    <cfRule type="expression" priority="3" dxfId="4">
-      <formula>H2=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I14">
-    <cfRule type="expression" priority="4" dxfId="4">
-      <formula>I2=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J14">
-    <cfRule type="expression" priority="5" dxfId="4">
-      <formula>J2=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K14">
-    <cfRule type="expression" priority="6" dxfId="4">
       <formula>K2=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L14">
-    <cfRule type="expression" priority="7" dxfId="4">
-      <formula>L2=1</formula>
+  <conditionalFormatting sqref="K3:R3">
+    <cfRule type="expression" priority="2" dxfId="4">
+      <formula>K3=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M14">
+  <conditionalFormatting sqref="K4:R4">
+    <cfRule type="expression" priority="3" dxfId="4">
+      <formula>K4=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5:R5">
+    <cfRule type="expression" priority="4" dxfId="4">
+      <formula>K5=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6:R6">
+    <cfRule type="expression" priority="5" dxfId="4">
+      <formula>K6=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7:R7">
+    <cfRule type="expression" priority="6" dxfId="4">
+      <formula>K7=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K8:R8">
+    <cfRule type="expression" priority="7" dxfId="4">
+      <formula>K8=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K9:R9">
     <cfRule type="expression" priority="8" dxfId="4">
-      <formula>M2=1</formula>
+      <formula>K9=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K10:R10">
+    <cfRule type="expression" priority="9" dxfId="4">
+      <formula>K10=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K11:R11">
+    <cfRule type="expression" priority="10" dxfId="4">
+      <formula>K11=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K12:R12">
+    <cfRule type="expression" priority="11" dxfId="4">
+      <formula>K12=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4791,16 +5862,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="68" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="78" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -4816,12 +5889,12 @@
       </c>
       <c r="C1" s="7" t="inlineStr">
         <is>
-          <t>Target timing</t>
+          <t>Planned date/week</t>
         </is>
       </c>
       <c r="D1" s="7" t="inlineStr">
         <is>
-          <t>Evidence</t>
+          <t>Exit evidence</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
@@ -4831,10 +5904,20 @@
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
-          <t>Exit gate</t>
+          <t>Dependencies</t>
         </is>
       </c>
       <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Approval requirements</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Exit criteria</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -4848,7 +5931,7 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Scope and requirements baseline</t>
+          <t>Scope, requirements and trade contract baseline</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
@@ -4858,22 +5941,32 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>Approved BR/FR, NFRs, RAID owners, target access design</t>
+          <t>Approved BR/FR/NFR decisions; trade source/version/correction semantics; named decision owners</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>Product Owner / Lead Engineer</t>
+          <t>Technical Project Manager / Product Owner</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>Sources, calculation scope, roles, and acceptance evidence agreed</t>
+          <t>TMP-001; TMP-002; TMP-003; TMP-006</t>
         </is>
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Product Owner and Trade Data Owner; role names proposed, identities TBD</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Business/product approval; no unowned critical assumption</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
         </is>
       </c>
     </row>
@@ -4885,7 +5978,7 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>Source and data design sign-off</t>
+          <t>Source and access design gate</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
@@ -4895,22 +5988,32 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Provider decision, source contracts, dictionary, integration test result</t>
+          <t>Market-data source decision; target identity/access design; dev workflow gate</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>Data Owner / Architect</t>
+          <t>Solution Architect / Market Data Owner</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>Provider rights and supported test runtime confirmed or scope explicitly remains prototype</t>
+          <t>TMP-005; TMP-007; TMP-023</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Platform/Security and Market Data Owner; no production access approval assumed</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>Provider approval or explicit prototype-only boundary; security review of design</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
         </is>
       </c>
     </row>
@@ -4922,7 +6025,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Engineering controls ready</t>
+          <t>Engineering controls and trade-history gate</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -4932,22 +6035,32 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>CI checks, deployment procedure, trade history reconciliation tests</t>
+          <t>CI evidence; trade correction/disappearance test; deployment control review</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>Lead Engineer</t>
+          <t>Lead Data Engineer / Technical Project Manager</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>Reviewed build/deploy and correction behavior proven</t>
+          <t>TMP-010; TMP-012</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Engineering owner and Product Control review of affected trade semantics</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>PR checks and correction behavior pass agreed acceptance criteria</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
         </is>
       </c>
     </row>
@@ -4969,27 +6082,84 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Dashboard UAT, end-to-end reconciliation, runbook, open risk acceptance</t>
+          <t>Supported-runtime tests; same-input rerun; reconciliation/UAT; runbook and support walkthrough</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>Product Owner / Operations</t>
+          <t>Product Control / Production Support</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Business and operations sign-off; no schedule unpause without separate production approval</t>
+          <t>TMP-016; TMP-021; TMP-022; TMP-024</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Product Control, QA, Production Support, and Sponsor go/no-go for prototype exit</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>Business acceptance and operational readiness review; schedule remains paused absent separate approval</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>M-05</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Optional dashboard and data sign-off</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>End Week 10 (optional follow-on)</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Approved reporting/data decisions; dashboard reconciliation and role access</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Product Owner / Product Control</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>TMP-008; TMP-014; TMP-020</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Product Owner, Product Control, and access owner</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Dashboard acceptance and business data approval; not a production release approval</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:I6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -5001,7 +6171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5009,15 +6179,18 @@
     <col width="68" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="76" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="72" customWidth="1" min="9" max="9"/>
+    <col width="72" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>RAID ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B1" s="7" t="inlineStr">
@@ -5042,15 +6215,30 @@
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
           <t>Mitigation / action</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
       <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Due date/week</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Escalation path</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -5084,15 +6272,30 @@
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
+          <t>Market Data Owner</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
           <t>Obtain provider/data-rights decision in Sprint 2; keep production scope blocked until approved source is selected.</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>Market Data Owner</t>
-        </is>
-      </c>
       <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>End Week 4 gate</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>No approved provider/rights or completeness owner by source gate.</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>Market Data Owner → Sponsor; Security/Legal/Data Governance as applicable.</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5126,15 +6329,30 @@
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
+          <t>Trade Data Owner</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
           <t>Agree cancellation/deletion semantics and implement two-snapshot reconciliation test before relying on external trade feed.</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t>Trade Data Owner</t>
-        </is>
-      </c>
       <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>End Week 6 gate</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>A two-snapshot comparison leaves a trade in Silver after authoritative removal/correction.</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>Trading Operations and Product Control → Sponsor if semantics affect positions/P&amp;L.</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5168,15 +6386,30 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
+          <t>Lead Data Engineer</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
           <t>Benchmark representative scale; establish reference ownership and incremental strategy from evidence.</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Lead Data Engineer</t>
-        </is>
-      </c>
       <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>Before any production scale decision</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>Representative-volume benchmark exceeds proposed runtime/cost or reference mapping is inconsistent.</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>Lead Engineer / Architect → TPM → Sponsor for scope/capacity decision.</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5210,15 +6443,30 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
           <t>Reserve decision owners at Sprint start; defer dashboard polish or extend by one sprint if critical access/decisions slip.</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
       <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>Weekly; reforecast each sprint</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Decision/access delay consumes the 2-point baseline headroom or threatens a gate.</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>TPM → Sponsor; defer optional dashboard/follow-on or approve added capacity.</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5252,15 +6500,30 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
+          <t>Product Owner</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
           <t>Product owner confirms before Sprint 1 exit; FX, derivatives, fees, and corporate actions stay out of scope.</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>Product Owner</t>
-        </is>
-      </c>
       <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>End Week 2</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Request includes FX, derivatives, fees, corporate actions, or additional instruments.</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>BA/PO and Product Control → Sponsor through change control.</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>To confirm</t>
         </is>
@@ -5294,15 +6557,30 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
+          <t>QA / Lead Engineer</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
           <t>Run and compare business keys/values in a supported runtime; retain evidence.</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>QA / Lead Engineer</t>
-        </is>
-      </c>
       <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 4 exit</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Same-input Job run evidence remains absent.</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>QA / Lead Engineer → TPM; hold idempotency acceptance.</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5336,15 +6614,30 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
+          <t>Lead Engineer / QA</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
           <t>Update stale test paths and assertions to the consolidated DDL, then rerun focused and full suite; application/test changes are outside this documentation task.</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>Lead Engineer / QA</t>
-        </is>
-      </c>
       <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 4 exit</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Tests still reference removed constraint scripts or focused failures persist.</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>QA / Lead Engineer → TPM; hold quality gate or document approved exception.</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5378,15 +6671,30 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
           <t>Record named decision owner and due date; keep job schedule paused until readiness gate.</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
       <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>End Week 2 decision log; before any non-dev release</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>No owner, target identity, data-rights decision, or test runtime is available.</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>TPM → Sponsor and accountable platform/data/security owner; release blocked.</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5420,22 +6728,37 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
           <t>Re-estimate at planning; the eight-week baseline has no reserve and is not a committed calendar date.</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
+          <t>Each sprint planning</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Committed role capacity or actual throughput differs from assumption.</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>TPM reforecasts with Sponsor; protect quality, reduce scope, or add approved time/capacity.</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
           <t>Proposed</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H10"/>
+  <autoFilter ref="A1:K10"/>
   <conditionalFormatting sqref="H2:H10">
     <cfRule type="expression" priority="1" dxfId="2">
       <formula>H2="Open"</formula>
@@ -6809,7 +8132,7 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>PLANNED</t>
+          <t>BLOCKED</t>
         </is>
       </c>
     </row>
@@ -8261,6 +9584,414 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Stakeholder role</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Responsibility</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Engagement approach</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Decision authority</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Communication frequency</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Assignment / evidence status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Project Sponsor</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Own business outcome, funding/capacity decisions, escalation and scope trade-offs.</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Steering summary, decision log and milestone gates.</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Approve project scope changes and prototype exit/go-no-go.</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Biweekly steering and milestone decisions (proposed).</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>Role required; named person not evidenced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Integrated plan, RAID, dependency management, governance, decisions, reporting and release readiness.</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Daily coordination; weekly workstream and RAID review; steering pack.</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Coordinate baseline and escalate; sponsor retains scope/budget authority.</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Daily / weekly / milestone cadence.</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Role assumed for interview plan; no actual allocation evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Business Analyst / Product Owner</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Business requirements, acceptance criteria, prioritization, UAT and reporting needs.</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Workshops, backlog refinement, sprint reviews and sign-off.</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Approve business requirements and acceptance within delegated scope.</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Part-time weekly; each sprint review (proposed).</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Part-time role assumed; name not evidenced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Solution Architect</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Architecture, integration contracts, data/security design and technical decisions.</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Design reviews, dependency/risk review and change impact.</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Recommend/approve design within architecture governance.</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>At design gates and material changes (proposed).</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Part-time role assumed; name not evidenced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineering</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>PySpark/SQL, Delta models, workflows, tests, CI/CD and technical runbooks.</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Daily stand-up, PR reviews, demos and incident triage.</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Technical implementation and evidence; not business P&amp;L sign-off.</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Daily; sprint cadence.</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>One lead engineer assumed; no named assignment evidenced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Product Control</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Challenge valuation/P&amp;L methodology, reconciliation tolerances and business acceptance.</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Calculation design review, exception review and UAT.</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Approve business calculation interpretation within delegated control framework.</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Design gate and weekly UAT window (proposed).</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Required role; participant not evidenced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Trading Operations</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Trade source delivery, completeness, corrections/cancellations and day-to-day operating process.</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Source-contract workshop, exception runbook and handover.</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Confirm operational source semantics and cutoff; not provider licensing.</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Weekly during source onboarding and handover (proposed).</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Required role; participant not evidenced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Information Security</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Review identity, least privilege, secrets, data classification and deployment controls.</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Architecture/security review and release readiness.</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Approve security controls under applicable policy.</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Design gate and before non-dev deployment (proposed).</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Required reviewer; approval not evidenced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Test strategy, test evidence, defect triage, regression, reconciliation and UAT coordination.</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Refinement, test reviews, sprint demos and release gate.</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Report test status and quality risk; does not approve business methodology.</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Part-time weekly; focused at test/release sprints.</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Part-time support assumed; name not evidenced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Production Support</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Monitoring, incident response, rerun/recovery, runbook, service ownership and handover.</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Operational design review, alert test and handover walkthrough.</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Accept operational readiness within support mandate.</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>At design gate and before handover (proposed).</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Required role; service owner not evidenced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Market Data Owner</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Provider selection, data rights, close definition, corrections, delivery SLA and completeness.</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Source decision and exception review.</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Approve market-data source and contractual/data-rights use.</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>At source selection and service review (proposed).</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Role required; owner/provider approval not evidenced.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F12"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -8660,6 +10391,2816 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:H9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Project Sponsor</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Business Analyst / Product Owner</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Solution Architect</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Data Engineering</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Product Control</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Trading Operations</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Information Security</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>Production Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Scope, funding and priority decisions</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Business/functional requirements and acceptance</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Architecture and technical data design</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Trade source contract and correction semantics</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Market-data provider and rights decision</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Security/access architecture review</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Build, unit tests and CI/CD implementation</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>P&amp;L methodology and reconciliation acceptance</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Release readiness and operational handover</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K10"/>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:K10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"A,R,C,I,A/R"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Workstream</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Proposed owner role</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Duration (sprint window weeks)</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Start week</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>End week</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Predecessors</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Story ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>TMP-01</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Baseline current implementation and confirm scope</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Technical Project Manager / Business Analyst-PO</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>M-01</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>TMP-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>TMP-01</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Approve business and functional requirements</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Technical Project Manager / Business Analyst-PO</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>TMP-001</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>M-01</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>TMP-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>TMP-01</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Set measurable non-functional and operational targets</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Technical Project Manager / Business Analyst-PO</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>TMP-002</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>M-01</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>TMP-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>TMP-02</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Document and validate existing solution architecture</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Solution Architect / Source Owners</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>N/A (historical / unscheduled)</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>N/A (actual dates not evidenced)</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>TMP-004</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>TMP-02</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Approve target security and environment architecture</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Solution Architect / Source Owners</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>TMP-002; TMP-003; TMP-004</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>M-02</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>TMP-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>TMP-02</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Confirm trade source contract and snapshot semantics</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Solution Architect / Source Owners</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>M-01</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>TMP-006</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>TMP-02</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Select and approve market-data source</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Solution Architect / Source Owners</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>TMP-002</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>M-02</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>TMP-007</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>TMP-02</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Approve physical data dictionary and retention model</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Solution Architect / Source Owners</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>TMP-006; TMP-007</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>M-05</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>TMP-008</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>TMP-03</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Maintain reproducible Databricks Asset Bundle development deployment</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Lead Data Engineer / Platform Owner</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>N/A (historical / unscheduled)</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>N/A (actual dates not evidenced)</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>TMP-009</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>TMP-03</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Add reviewed CI checks and controlled deployment promotion</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Lead Data Engineer / Platform Owner</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>TMP-005; TMP-009</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>M-03</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>TMP-010</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>TMP-04</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Ingest synthetic trade snapshot into Bronze</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineering / Trading Operations</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>N/A (historical / unscheduled)</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>N/A (actual dates not evidenced)</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>TMP-006</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>TMP-011</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>TMP-04</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Resolve trade snapshot disappearance and historical correction controls</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Data Engineering / Trading Operations</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>TMP-006; TMP-011</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>M-03</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>TMP-012</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>TMP-04</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Ingest and retain daily market-price history</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineering / Trading Operations</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>N/A (historical / unscheduled)</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>N/A (actual dates not evidenced)</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>TMP-007</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>TMP-013</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>TMP-04</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Harden price source decision and completeness exception process</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Data Engineering / Trading Operations</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>TMP-007; TMP-013</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>M-05</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>TMP-014</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>TMP-04</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Validate Silver trades and prices with reject history</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineering / Trading Operations</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>N/A (historical / unscheduled)</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>N/A (actual dates not evidenced)</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>TMP-011; TMP-013</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>TMP-015</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>TMP-06</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Run Spark/Delta integration and end-to-end rerun validation</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>QA / Product Control / Data Engineering</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>TMP-015</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>M-04</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>TMP-016</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>TMP-05</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Build cumulative daily positions and exact-date valuation</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Data Engineering / Product Control</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>N/A (historical / unscheduled)</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>N/A (actual dates not evidenced)</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>TMP-015</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>TMP-017</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>TMP-05</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Calculate daily cash-equity mark-to-market P&amp;L</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Data Engineering / Product Control</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>N/A (historical / unscheduled)</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>N/A (actual dates not evidenced)</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>TMP-017</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>TMP-018</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>TMP-06</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Provide notebook and SQL operational reporting</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>QA / Product Control / Data Engineering</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>N/A (historical / unscheduled)</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>N/A (actual dates not evidenced)</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>TMP-018</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>TMP-019</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>TMP-06</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Deliver user-accepted trading and P&amp;L dashboard MVP</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>QA / Product Control / Data Engineering</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>TMP-002; TMP-008; TMP-018; TMP-019</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>M-05</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>TMP-020</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>TMP-06</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Maintain deterministic unit and transformation tests</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>QA / Product Control / Data Engineering</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>M-04</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>TMP-021</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>TMP-06</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Complete independent position/P&amp;L reconciliation and UAT</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>QA / Product Control / Data Engineering</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>TMP-016; TMP-018</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>M-04</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>TMP-022</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>TMP-07</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Operate the dev workflow with controlled scheduling</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Technical Project Manager / Production Support</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>TMP-009</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>M-02</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>PARTIALLY IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>TMP-023</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>TMP-07</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Create support runbook, alerting, and handover</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Technical Project Manager / Production Support</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>TMP-003; TMP-019; TMP-022; TMP-023</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>M-04</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>TMP-024</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J25"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="76" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Delivery role</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Capacity assumption</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Workstream allocation</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Estimated effort (person-days)</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Estimate basis</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Capacity constraints / status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>0.4 FTE; 4 person-days per 2-week sprint</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Integrated plan, dependencies, RAID, decisions, reporting and readiness</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Baseline effort = capacity per sprint × 4 sprints</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>Proposed capacity; no named assignment or competing demand verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Lead Data Engineer</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>1.0 FTE; 10 person-days per sprint</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>PySpark/SQL, Delta, tests, Bundle/CI and technical runbooks</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Baseline effort = capacity per sprint × 4 sprints</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Single-engineer bottleneck; 10 SP/sprint planning cap is an assumption, not measured velocity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Business Analyst / Product Owner</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>0.3 FTE; 3 person-days per sprint</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Requirements, acceptance criteria, prioritization, UAT</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Baseline effort = capacity per sprint × 4 sprints</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Part-time decision availability; response latency can block approval gates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Solution Architect</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>0.2 FTE; 2 person-days per sprint</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Architecture, source integration, data and security design reviews</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Baseline effort = capacity per sprint × 4 sprints</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Part-time; review windows must be booked around design gates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>0.3 FTE; 3 person-days per sprint</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Test planning, supported-runtime tests, defect triage, UAT support</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Baseline effort = capacity per sprint × 4 sprints</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Spark/Delta environment access is a prerequisite; availability unconfirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Product Control</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>0.1 FTE; 1 person-day per sprint</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Calculation methodology, materiality, reconciliation and acceptance</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Baseline effort = capacity per sprint × 4 sprints</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Business calculation owner and tolerance are not identified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Trading Operations</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>0.1 FTE; 1 person-day per sprint</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Source contract, completeness/correction rules and operating process</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Baseline effort = capacity per sprint × 4 sprints</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Source owner/cutoff not evidenced; availability is proposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Information Security</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>0.1 FTE; 1 person-day per sprint</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Access, identity, data classification and release review</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Baseline effort = capacity per sprint × 4 sprints</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Security reviewer and applicable controls must be confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Production Support</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>0.1 FTE; 1 person-day per sprint</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Monitoring, rerun/recovery process, operational acceptance and handover</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Baseline effort = capacity per sprint × 4 sprints</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Support owner, hours, SLA and escalation channel not evidenced.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F10"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="64" customWidth="1" min="5" max="5"/>
+    <col width="78" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Participants</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Outputs</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Escalation route</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Engineering stand-up</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Surface progress, next steps, blockers and cross-branch dependencies; keep it to delivery decisions.</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>TPM, Data Engineering, BA/PO, QA as needed</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Daily, 15 minutes (proposed).</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Updated actions, blockers and dependency owner/date.</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>Blocker unresolved by next working day → TPM; scope/date/decision blockage → Sponsor or accountable owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Workstream review</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Review trade, price, platform, calculation, test and reporting work against sprint outcomes.</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>TPM, workstream leads, BA/PO, Architect, QA and invited control/operations owners</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Weekly (proposed).</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Forecast, dependency changes, decisions, acceptance evidence.</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Cross-workstream conflict → TPM; architecture/security decision → review owner; scope trade-off → Sponsor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>RAID and change review</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Reassess probability/impact, triggers, owners, due dates and change requests.</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>TPM, story owners, BA/PO, Architect, QA; Sponsor for high impact</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Weekly and at material change (proposed).</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>RAID actions, change-impact assessment, decision-log updates.</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>High-impact / near-term trigger → Sponsor and affected control owner immediately; unresolved policy risk blocks release.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Architecture and security review</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Review provider interface, data contracts, UC permissions, identity, secrets and deployment boundary.</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Solution Architect, Information Security, Data Engineering, Platform owner, Production Support</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>At design baseline and before material change or non-dev deployment.</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Decision record, approved design constraints, security actions.</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Unapproved data rights/access or policy exception → accountable Security/Architecture authority; no production promotion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Steering update</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Give concise evidence-based status and obtain scope/capacity decisions.</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Sponsor, TPM, BA/PO, Architect, engineering and relevant business/control owners</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Biweekly or at milestone gates (proposed).</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>RAG status, milestone forecast, top RAID, decisions, change approvals.</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Sponsor decision; record outcome and effect on scope, capacity, schedule and risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Milestone approval gate</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Confirm specific acceptance evidence before entering dependent work or presenting readiness.</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Named accountable milestone owner and required approvers listed in Milestone Tracker.</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>End of Weeks 2, 4, 6, 8; optional Week 10 follow-on.</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Approve / reject / conditional approval, evidence links, actions and owner/date.</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Missing approval or failed criterion → hold dependent work/release and escalate to Sponsor; do not infer approval from demo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Release readiness review</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Assess source, security, quality, monitoring, recovery, support and business acceptance before any schedule activation.</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Sponsor, Product Control, QA, Security, Production Support, TPM, Architect and Data Engineering</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Once before any non-dev release or schedule unpause; repeat after material scope change.</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Readiness checklist, explicit go/no-go, residual risk acceptance and rollback plan.</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Any critical control/source/UAT/support gap → no-go; Sponsor cannot waive policy-owner approval.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="66" customWidth="1" min="7" max="7"/>
+    <col width="64" customWidth="1" min="8" max="8"/>
+    <col width="58" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Change request</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Request / status</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Business justification</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Scope impact</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Schedule impact</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Resource impact</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Risk impact</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Approver</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>CR-LOG</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>No actual change request evidenced as of 2026-10-14</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>No submitted/approved change is recorded in the repository evidence.</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>No approved change to current USD cash-equity prototype scope.</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>No actual schedule impact recorded.</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>No approved resource impact recorded.</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>Any new request is assessed through change control; multi-currency example is hypothetical only.</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>No change decision recorded; use this register for new requests.</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>Not applicable; approver roles are defined in governance/RACI.</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="78" customWidth="1" min="4" max="4"/>
+    <col width="72" customWidth="1" min="5" max="5"/>
+    <col width="82" customWidth="1" min="6" max="6"/>
+    <col width="72" customWidth="1" min="7" max="7"/>
+    <col width="76" customWidth="1" min="8" max="8"/>
+    <col width="82" customWidth="1" min="9" max="9"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Scenario ID</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Delivery impact</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Critical dependencies</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Mitigation</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Escalation</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Contingency</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Decision required</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>SC-A</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>HYPOTHETICAL: market-data provider approval is delayed</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Provider rights or source-owner approval is not available by the Sprint 2 source gate.</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Production data path and price SLA remain unapproved; integration/UAT evidence is limited to existing prototype provider and deterministic fixtures; downstream valuation sign-off is at risk.</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Market Data Owner decision; contract/data-rights review; interface and price definition; fixture availability.</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>Continue provider-neutral contract tests and synthetic fixture work; isolate adapter; keep Yahoo Finance prototype-only; do not claim a production feed.</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>TPM raises at weekly RAID and immediately to Sponsor/Market Data Owner if the Week 4 gate is threatened; Security/Legal/Data Governance consulted as required.</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Defer production source integration and dashboard UAT; use optional Sprint 5 or rebaseline after decision; do not bypass licensing.</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>Sponsor accepts scope/date trade-off; authorized Market Data Owner approves provider, rights, and service expectations.</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>Hypothetical only; not an actual incident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>SC-B</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>HYPOTHETICAL: multi-currency P&amp;L requested during implementation</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Business requests non-USD P&amp;L after the USD prototype scope is baselined.</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Adds FX source/rates, currency/date conventions, conversion policy, model dimensions, decimal/rounding rules, valuation/P&amp;L logic, tests, dashboard filters, and control sign-off; 8-week baseline is not assumed to absorb it.</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Currency and FX business rules; approved FX provider; accounting/Product Control policy; reference mapping and data model review.</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Log a change request; BA/Architect/Data Engineering/QA/Product Control estimate impact and identify affected BR/FR, tables, stories and tests; keep USD-only baseline unchanged pending approval.</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>TPM presents options and impact at steering; Sponsor owns scope/capacity trade-off; Product Control and architecture/security owners approve their domains.</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>Defer multi-currency to separately estimated release or swap explicitly lower-priority dashboard scope; add capacity/sprint only after resource confirmation.</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Approve, reject, or defer by named Sponsor with documented Product Control methodology approval; update baseline and traceability before work starts.</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>Hypothetical only; no such request is evidenced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>SC-C</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>HYPOTHETICAL: position or P&amp;L reconciliation identifies incorrect results</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Independent SQL/UAT reconciliation finds a material quantity, valuation, or P&amp;L mismatch.</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Affected output is not accepted; any dependent dashboard/demo/release is held; assess impacted dates/books/instruments and downstream users before reuse.</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Reproducible input snapshot/run ID; expected calculation; defect severity/materiality; Product Control decision.</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Stop promotion; preserve run and input evidence; compare Bronze→Silver→Gold by business key; classify source, transform, calendar, price, or methodology defect; create defect and regression test; rerun and reconcile corrected scope.</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>QA alerts TPM and Product Control immediately for material financial mismatch; TPM escalates release impact to Sponsor and Production Support; security/data incident path if exposure or integrity breach is suspected.</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>Rollback/retain last accepted dataset where supported; mark output unavailable rather than zero or silently corrected; replan dependent milestones after root cause and fix.</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>Product Control accepts calculation result/tolerance; QA confirms regression; release authority records go/no-go and residual risk.</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>Hypothetical only; not an actual incident.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -23033,7 +27574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -23078,7 +27619,7 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Project Initiation and Business Analysis</t>
+          <t>Project Mobilisation and Business Requirements</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
@@ -23105,7 +27646,7 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>Requirements and Acceptance Criteria</t>
+          <t>Architecture, Data Contracts and Governance Design</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
@@ -23132,7 +27673,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Solution Architecture and Technical Design</t>
+          <t>Platform Engineering and CI/CD</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -23159,7 +27700,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Data Sourcing and Data Modelling</t>
+          <t>Trade and Market Data Integration</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -23186,7 +27727,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Platform Setup and CI/CD</t>
+          <t>Positions and Daily P&amp;L</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -23213,7 +27754,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Trade Data Ingestion</t>
+          <t>Testing, Reconciliation and Reporting</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -23240,7 +27781,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Market Price Ingestion</t>
+          <t>Release Readiness and Operational Handover</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -23259,170 +27800,8 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>TMP-EP08</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Silver Data Processing</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>Planning epic; mixed current-state evidence and target backlog. See linked story implementation status.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>TMP-EP09</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Position Calculation</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>Planning epic; mixed current-state evidence and target backlog. See linked story implementation status.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>TMP-EP10</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>P&amp;L Calculation</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>Planning epic; mixed current-state evidence and target backlog. See linked story implementation status.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>TMP-EP11</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Reporting and Dashboard</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>Planning epic; mixed current-state evidence and target backlog. See linked story implementation status.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>TMP-EP12</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Testing and Reconciliation</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>Planning epic; mixed current-state evidence and target backlog. See linked story implementation status.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>TMP-EP13</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Deployment, Monitoring and Handover</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>Planning epic; mixed current-state evidence and target backlog. See linked story implementation status.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E14"/>
+  <autoFilter ref="A1:E8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -23610,7 +27989,7 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>TMP-EP02</t>
+          <t>TMP-EP01</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
@@ -23685,7 +28064,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>TMP-EP02</t>
+          <t>TMP-EP01</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -23760,7 +28139,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>TMP-EP03</t>
+          <t>TMP-EP02</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -23827,7 +28206,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>TMP-EP03</t>
+          <t>TMP-EP02</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -23865,7 +28244,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>Sprint 1</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
@@ -23902,7 +28281,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>TMP-EP04</t>
+          <t>TMP-EP02</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -23938,7 +28317,11 @@
           <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
-      <c r="J7" s="9" t="inlineStr"/>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
           <t>BR-001; BR-003</t>
@@ -23969,7 +28352,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>TMP-EP04</t>
+          <t>TMP-EP02</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -24044,7 +28427,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>TMP-EP04</t>
+          <t>TMP-EP02</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -24077,12 +28460,12 @@
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>PARTIALLY IMPLEMENTED</t>
+          <t>NOT VERIFIED</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr">
@@ -24119,7 +28502,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>TMP-EP05</t>
+          <t>TMP-EP03</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -24186,7 +28569,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>TMP-EP05</t>
+          <t>TMP-EP03</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -24261,7 +28644,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>TMP-EP06</t>
+          <t>TMP-EP04</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -24332,7 +28715,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>TMP-EP06</t>
+          <t>TMP-EP04</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -24407,7 +28790,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>TMP-EP07</t>
+          <t>TMP-EP04</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -24478,7 +28861,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>TMP-EP07</t>
+          <t>TMP-EP04</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -24516,7 +28899,7 @@
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr">
@@ -24553,7 +28936,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>TMP-EP08</t>
+          <t>TMP-EP04</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -24624,7 +29007,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>TMP-EP08</t>
+          <t>TMP-EP06</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -24662,7 +29045,7 @@
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
@@ -24699,7 +29082,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>TMP-EP09</t>
+          <t>TMP-EP05</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -24770,7 +29153,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>TMP-EP10</t>
+          <t>TMP-EP05</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -24841,7 +29224,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>TMP-EP11</t>
+          <t>TMP-EP06</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -24912,7 +29295,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>TMP-EP11</t>
+          <t>TMP-EP06</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -24945,12 +29328,12 @@
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>PLANNED</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>Sprint 4</t>
+          <t>Sprint 5</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
@@ -24987,7 +29370,7 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>TMP-EP12</t>
+          <t>TMP-EP06</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -25023,7 +29406,11 @@
           <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
-      <c r="J22" s="8" t="inlineStr"/>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
           <t>BR-001; BR-002; BR-003; BR-004; BR-005; BR-007</t>
@@ -25054,7 +29441,7 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>TMP-EP12</t>
+          <t>TMP-EP06</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -25129,7 +29516,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>TMP-EP13</t>
+          <t>TMP-EP07</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -25165,7 +29552,11 @@
           <t>PARTIALLY IMPLEMENTED</t>
         </is>
       </c>
-      <c r="J24" s="8" t="inlineStr"/>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
           <t>BR-007; BR-008</t>
@@ -25200,7 +29591,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>TMP-EP13</t>
+          <t>TMP-EP07</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -25279,13 +29670,16 @@
     <cfRule type="expression" priority="3" dxfId="2">
       <formula>I2="PLANNED"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
-      <formula>I2="TO BE CONFIRMED"</formula>
+    <cfRule type="expression" priority="4" dxfId="2">
+      <formula>I2="BLOCKED"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="3">
+      <formula>I2="NOT VERIFIED"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation sqref="I2:I25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"IMPLEMENTED,PARTIALLY IMPLEMENTED,PLANNED,TO BE CONFIRMED"</formula1>
+      <formula1>"IMPLEMENTED,PARTIALLY IMPLEMENTED,PLANNED,BLOCKED,NOT VERIFIED"</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"High,Medium,Low,Must,Should"</formula1>
